--- a/sacc-meta-analysis/data/SACC_master_extraction.xlsx
+++ b/sacc-meta-analysis/data/SACC_master_extraction.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="overlap" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vocab_outcomes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grade" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +458,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PubMed searched 2026-10-05 with the exact Table S1 strategy (esearch count); all 22 inventory records retrieved by it</t>
+          <t>PubMed (MEDLINE), Table S1 strategy, searched 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Not yet run (no access from build environment)</t>
+          <t>Not searched: no subscription/API key available (HTTP 401/403)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Not yet run</t>
+          <t>Not searched: institutional subscription required</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not yet run</t>
+          <t>Not searched: institutional subscription required</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Not yet run</t>
+          <t>Not searched: site unreachable from the analysis environment</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Not yet run</t>
+          <t>Not searched: full records require institutional login</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Not yet run</t>
+          <t>Not searched: unreachable</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Earlier web-search inventory (22 records) fully contained in the PubMed result; citation chasing of included studies not yet done</t>
+          <t>Europe PMC title/abstract search (297 records, incl. preprints and Chinese Biological Abstracts) and Crossref bibliographic search (15 relevant-titled records not in PubMed/Europe PMC), 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Single database so far</t>
+          <t>Europe PMC records already retrieved by PubMed</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Interim (PubMed only): titles screened by one AI-assisted reviewer on 2026-10-05; second human screener pending</t>
+          <t>337 PubMed + 30 Europe PMC-only + 15 Crossref-only records</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Interim (PubMed only)</t>
+          <t>Case reports, reviews, experimental studies, risk/epidemiological studies, preprint duplicates of included papers, retracted preprint</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22 inventory reports (minus 2 epidemiological risk studies catalogued from abstracts) + 9 newly identified (Feng 2015, Wu 2021, Chai 2026, Chen 2016, Yang DH 2014, Ruan 2013, Yang XG 2021, Zhang R 1998, Zalata 2005)</t>
+          <t>20 inventory reports + 9 from PubMed screen + Ge 2023, Zhou 2025, Pan 2022 (Europe PMC) + Farid 2006 (Crossref)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wang M 2014, Wang M 2016, NCG 1986, Madbouly 2007, Liu 2013, Zhang W 2012 (CT), Chen 2016, Yang DH 2014, Ruan 2013, Yang XG 2021, Zhang R 1998, Zalata 2005 (publisher/CNKI access needed)</t>
+          <t>Wang M 2016, NCG 1986, Madbouly 2007, Zhang W 2012, Chen 2016, Yang DH 2014, Ruan 2013, Yang XG 2021, Zhang R 1998, Zalata 2005, Farid 2006</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zheng 2023, Wang Z 2020, Wang W 2020/2021/2023, Pan 2020, Cheng 2023, Chai 2026, Li 2024, Zhang 2023, Zhu 2024, Yang 2023, Wu 2021, Feng 2015, Pan 2023, Yu 2023 (genomic), Liu XF 2023</t>
+          <t>17 previously + Wang M 2014, Liu 2013 (KoreaScience OA), Ge 2023, Zhou 2025, Pan 2022 (Research Square)</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liu XF 2023: no CRC-specific SACC-versus-NSACC data (malignancy spectrum among S. japonicum patients)</t>
+          <t>Liu XF 2023 (no CRC-specific comparison); Liu 2013 (no non-schistosomal comparator)</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16 reports from 9 overlap groups: 7 independent comparative cohorts (14 reports incl. 5 biomarker reports from the Qingpu cohort), 1 SACC-only cohort, 1 external-comparator genomic study</t>
+          <t>20 reports from 12 institutions/groups: 10 comparative cohorts (G1-G6, G10, G11, G14, G15), 1 SACC-only cohort (G9), 1 external-comparator genomic study</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reports contributing to at least one pooled estimate: Zheng 2023, Wang Z 2020, Yang 2023, Wang W 2020, Li 2024, Zhu 2024, Zhang 2023, Wu 2021, Feng 2015 (7 independent comparative cohorts) + Cheng 2023 (within-SACC pooled LN metastasis)</t>
+          <t>Reports in &gt;=1 pooled estimate: Zheng 2023, Wang Z 2020, Yang 2023, Wang W 2020, Li 2024, Zhu 2024, Zhang 2023, Wu 2021, Feng 2015, Wang M 2014, Ge 2023 (9 independent comparative cohorts) + Cheng 2023 (within-SACC)</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Zhongshan Hospital, Fudan University / Qingpu Branch (co-authors overlap with G3)</t>
+          <t>Department of Pathology, Qingpu Branch of Zhongshan Hospital, Fudan University</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Shanghai (Qingpu)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dept of Gastroenterological Surgery, West China Hospital, Sichuan University</t>
+          <t>Department of Gastroenterological Surgery, West China Hospital, Sichuan University</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S. japonicum (to verify)</t>
+          <t>S. japonicum presumed</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Potentially eligible - full text not retrieved</t>
+          <t>Included (survival only; matched on age, sex and stage)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Abstract only (PubMed); no HR in abstract</t>
+          <t>Full text read 2026-10-05 (KoreaScience OA PDF via Unpaywall)</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>APJCP full text hosted on KoreaScience/WAOCP (not reachable). Matched on age, sex and stage: survival only.</t>
+          <t>Adjusted HRs in Table 3. SACC definition not stated. Matched design invalidates stage/sex/age comparisons.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Excluded from comparative synthesis (no comparator) - full text not retrieved</t>
+          <t>Excluded at full text (no non-schistosomal comparator)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>n from title</t>
+          <t>Full text read 2026-10-05 (KoreaScience OA PDF)</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -4081,738 +4081,6 @@
       <c r="X26" t="inlineStr">
         <is>
           <t>286 of the 351 G3 patients.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Chen2016</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Chen Y</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>[Expression difference of DNA mismatch repair gene hMLH1 and hMSH2 between schistosomiasis-associated colorectal cancer and sporadic colorectal cancer]</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Zhonghua Wei Chang Wai Ke Za Zhi</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>19(1):75-9</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>26797844</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Zhejiang Cancer Hospital</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Hangzhou, Zhejiang</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>S. japonicum (to verify)</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Retrospective cohort (Chinese)</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Age, platelets, WBC, differentiation, hMLH1/hMSH2</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>G13-Hangzhou-ZJCancer</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Molecular evidence table</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Requires CNKI/publisher access</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>YangDH2014</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Yang DH</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[Relationship between multi-gene proteins in colorectal carcinoma complicated with chronic schistosomiasis: an immunohistochemical study by using tissue microarray techniques]</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Zhongguo Xue Xi Chong Bing Fang Zhi Za Zhi</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>26(4):405-9</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>25434139</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>S. japonicum (to verify)</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Comparative IHC study (Chinese)</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>p53, COX-2, Bax, c-myc</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Molecular evidence table</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Requires CNKI/publisher access</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Ruan2013</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ruan SL</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[Expression of vascular growth factors in intestinal tissues in colorectal carcinoma patients with schistosomiasis japonica]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Zhongguo Xue Xi Chong Bing Fang Zhi Za Zhi</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>25(3):250-4</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>24024441</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>S. japonicum (to verify)</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Comparative expression study (Chinese)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>PD-ECGF, VEGF</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Molecular evidence table</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Requires CNKI/publisher access</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>YangXG2021</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Yang XG</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[Expression and clinicopathological significance of Bcl-2 and Bax genes in colorectal cancer patients complicated with schistosomiasis]</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Zhongguo Xue Xi Chong Bing Fang Zhi Za Zhi</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>33(2):148-153</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>34008361</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>10.16250/j.32.1374.2020320</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>First Affiliated Hospital of Dali University</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Dali, Yunnan</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>S. japonicum (to verify)</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Random samples of SACC and CRC (Chinese)</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Bcl-2, Bax</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Molecular evidence table</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Requires CNKI/publisher access</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ZhangR1998</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Zhang R</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>p53 gene mutations in rectal cancer associated with schistosomiasis japonica in Chinese patients</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Cancer Lett</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>131(2):215-21</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>9851256</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>10.1016/s0304-3835(98)00154-2</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>S. japonicum (to verify)</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Comparative mutation study (rectal cancer)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>TP53 mutation spectrum</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Molecular evidence table</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Requires CNKI/publisher access</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Zalata2005</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Zalata KR</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>p53, Bcl-2 and C-Myc expressions in colorectal carcinoma associated with schistosomiasis in Egypt</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Cell Oncol</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>27(4):245-53</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>16308474</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>10.1155/2005/547010</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>PMC4615168</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Mansoura University (verify)</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>S. mansoni</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Comparative IHC study</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>p53, Bcl-2, c-Myc</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Separate species stratum (S. mansoni)</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Potentially eligible - full text not retrieved (identified by PubMed search 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>PMID confirmed</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Abstract only</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>PMC page behind a challenge; retry manually</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5435,7 +4703,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5450,12 +4718,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WangM2016 and Liu2013 (same hospital)</t>
+          <t>WangM2016 (same department, 2009-07 to 2012-07, SACC only); Liu2013 (endoscopy series)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNRESOLVED: full text not retrieved; not analysed</t>
+          <t>RESOLVED: survival only (adjusted HRs); WangM2016 not retrieved</t>
         </is>
       </c>
     </row>
@@ -5604,6 +4872,117 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>Molecular map only</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Xiangya Hospital, Changsha</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2014-01 to 2019-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6025 (94 matched)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RESOLVED: separate cohort G14 (preprint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Affiliated Hospital of Jiujiang University</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2013-07 to 2024-08</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NR (~95)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Separate cohort G15; qualitative only (no denominators)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pan2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Qingpu Branch of Zhongshan Hospital</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2008-01 to 2016-08</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WangW2020 (338 of 351)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RESOLVED: MET only</t>
         </is>
       </c>
     </row>
@@ -5835,6 +5214,1054 @@
       <c r="A31" t="inlineStr">
         <is>
           <t>recurrence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>certainty</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>risk_of_bias</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>inconsistency</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>indirectness</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>imprecision</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>publication_bias</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>upgrade</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OS - Adjusted</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Start low (observational). Three small cohorts (197 SACC); I2 57% and leave-one-out estimates range 1.76-2.86; few events and wide CI. HR &gt;2 not used to upgrade because of the downgrades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OS - Unadjusted</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>very serious</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Opposite directions across cohorts (I2 87%); one estimate derived from a log-rank P in a 100-patient subset; CI includes harm and benefit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DFS - Adjusted</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>I2 67%; CI 0.93-3.07 includes no effect; three cohorts with different covariate sets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DFS - Unadjusted</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Two cohorts; unadjusted for stage; both attenuate after adjustment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stage III-IV</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>I2 61%; CI 0.56-1.07; significant without the preprint cohort (OR 0.84, 0.74-0.97) but not without the largest cohort (OR 0.68, 0.33-1.40).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lymph-node metastasis</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Five cohorts; I2 49%; CI 0.76-1.23 excludes large differences in either direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Distant metastasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Four cohorts (I2 12%) using stage IV as proxy; one report stated that metastatic disease was excluded; CI 0.58-1.13 includes appreciable benefit and no effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pT3-T4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>I2 69%; depth definitions differ (pathological vs infiltration-depth categories).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Male sex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Seven cohorts, I2 0%, robust to every sensitivity analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Magnitude heterogeneous (I2 96%) but every cohort older or similar; not downgraded for inconsistency of direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Age &gt; 60 years</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Five cohorts, all in the same direction; heterogeneity in magnitude only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rectal location</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Small effect (OR 1.17) that is lost without the largest cohort (OR 1.06, 0.88-1.26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sigmoid location</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Three cohorts, I2 0%, no difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Right-sided colon</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>I2 50%; CI includes no effect; side definitions differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Poor differentiation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>very serious</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>I2 88%; definitions differ (one cohort includes mucinous/signet-ring); one implausible cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mucinous histology</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>very serious</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Three small cohorts; wide CI 0.61-3.47.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vascular invasion</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Five cohorts, I2 17%, no difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Perineural invasion</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Five cohorts, I2 6%, no difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tumour budding</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>very serious</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Two cohorts with different cut-offs; I2 90%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tumour size &gt;= 5 cm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>very serious</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Two small cohorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KRAS mutation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very low</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>not serious</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>undetected (k&lt;10)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Two cohorts with different assays; only the larger cohort significant; KRAS status unknown in 41-60% of the largest cohort.</t>
         </is>
       </c>
     </row>
@@ -7886,7 +8313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8049,7 +8476,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -8136,7 +8563,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -8223,7 +8650,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -8310,7 +8737,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -8397,7 +8824,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -8484,7 +8911,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -8494,7 +8921,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Table 1 pN gives 260 (178+82) for SACC; Table S4 Yes/No used (internally consistent: 490+261=751)</t>
+          <t>Table 1 pN gives 260 (178+82) for SACC; Table S4 Yes/No used (internally consistent: 490+261=751); Adjudicated: second extractor used Table 1 (260/751); Table S4 retained (source inconsistency, difference of one patient)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8998,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -8654,7 +9081,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -8741,7 +9168,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -8824,7 +9251,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -8907,7 +9334,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -8994,7 +9421,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -9077,7 +9504,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -9160,7 +9587,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -9243,7 +9670,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -9330,7 +9757,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -9413,7 +9840,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -9496,7 +9923,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -9579,7 +10006,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -9662,7 +10089,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -9749,7 +10176,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -9832,7 +10259,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -9915,7 +10342,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -9998,7 +10425,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -10081,7 +10508,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -10168,7 +10595,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -10255,7 +10682,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -10342,7 +10769,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -10425,7 +10852,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -10508,7 +10935,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -10591,7 +11018,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -10674,7 +11101,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -10757,7 +11184,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -10840,7 +11267,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -10923,7 +11350,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -11006,7 +11433,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -11089,7 +11516,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -11176,7 +11603,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -11259,7 +11686,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -11342,7 +11769,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -11425,7 +11852,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -11508,7 +11935,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -11591,7 +12018,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -11674,7 +12101,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -11757,7 +12184,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -11840,7 +12267,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -11923,7 +12350,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -12006,7 +12433,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -12093,7 +12520,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -12176,7 +12603,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -12259,7 +12686,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -12342,7 +12769,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -12425,7 +12852,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -12508,7 +12935,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -12595,7 +13022,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -12678,7 +13105,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -12761,7 +13188,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -12844,7 +13271,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -12927,7 +13354,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -13014,7 +13441,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -13101,7 +13528,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -13188,7 +13615,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -13275,7 +13702,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -13362,7 +13789,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -13449,7 +13876,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -13536,7 +13963,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -13623,7 +14050,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -13710,7 +14137,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -13793,7 +14220,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -13876,7 +14303,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -13959,7 +14386,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -14042,7 +14469,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -14125,7 +14552,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -14212,7 +14639,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -14295,7 +14722,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -14306,6 +14733,702 @@
       <c r="Q76" t="inlineStr">
         <is>
           <t>Row counts and percentages disagree for SRC vs mucinous; combined count is consistent with 16 adenocarcinomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>male_sex</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (unmatched cohort)</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>age_over_60</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2973</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Results text (79, 84.0% vs 2973, 49.3% 'over 60')</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Preprint. Adjudicated: text values (consistent with its percentages) used; Table 1 bands give 78 vs 2787 for &gt;60 (61+), so the text cut-off is &gt;=60</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>rectal_location</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (location)</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sigmoid_location</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (location)</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>right_sided</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (location)</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>advanced_stage_III_IV</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3085</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>calculated_from_raw</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (TNM III+IV)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>distant_metastasis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>calculated_from_raw</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Table 1 (TNM IV)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Preprint, not peer reviewed. Stage IV used as distant metastasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Feng2015</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>distant_metastasis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>calculated_from_raw</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Feng 2015 World J Gastroenterol (PMC4476884); Table 1 (tumour stage IV)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Stage IV used as distant metastasis; added at adjudication (identified by second extractor)</t>
         </is>
       </c>
     </row>
@@ -14328,7 +15451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14573,7 +15696,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -14683,7 +15806,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -14797,7 +15920,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -14911,7 +16034,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -15033,7 +16156,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -15147,7 +16270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -15269,7 +16392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -15383,7 +16506,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -15497,7 +16620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -15611,7 +16734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -15725,7 +16848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -15839,7 +16962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -15850,6 +16973,120 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>Exploratory; single cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>66.13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9.23</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>58.35</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mean_SD</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Results (clinical baseline), unmatched cohort</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Preprint</t>
         </is>
       </c>
     </row>
@@ -15869,7 +17106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16088,7 +17325,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -16201,7 +17438,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -16314,7 +17551,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -16423,7 +17660,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -16536,7 +17773,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -16645,7 +17882,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -16758,7 +17995,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -16867,7 +18104,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -16980,7 +18217,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -17089,7 +18326,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -17100,6 +18337,357 @@
       <c r="W11" t="inlineStr">
         <is>
           <t>Derived (Tierney 2007): z=2.226, events=39, V=D*n1*n2/(n1+n2)^2=9.559; direction from 5-y OS 68.9% vs 46.4% (SACC better). Follow-up subset 2012-2013 only; deaths 18/43 vs 21/57 are hard to reconcile with the 5-y survival figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.162</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.262</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.705</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Propensity-matched 1:1 on sex, age, tumour location, year of surgery, TNM stage, preoperative chemotherapy (HR itself unadjusted)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NSACC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>derived_Tierney_logrank_P</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Ge 2023 Research Square preprint (doi:10.21203/rs.3.rs-2831569/v1); Results (prognostic data), Fig. 4: deaths 35 vs 18, log-rank P=0.005</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Derived (Tierney 2007): z=2.807, events=53, V=13.25. Matched cohort. Preprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.661</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.458</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9.193</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pathologic T, N and TNM stage; cohort matched 1:1 on age, sex and stage</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NSACC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Wang M 2014 Asian Pac J Cancer Prev (KoreaScience PDF); Table 3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rectal cancer, laparoscopic TME, 2009; SACC definition not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DFS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.147</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.359</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pathologic N and TNM stage; matched on age, sex and stage</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NSACC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Wang M 2014 Asian Pac J Cancer Prev (KoreaScience PDF); Table 3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>As for OS</t>
         </is>
       </c>
     </row>
@@ -17119,7 +18707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17338,7 +18926,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -17443,7 +19031,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -17548,7 +19136,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -17657,7 +19245,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -17766,7 +19354,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -17871,7 +19459,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -17976,7 +19564,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -18089,7 +19677,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -18202,7 +19790,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -18315,7 +19903,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -18428,7 +20016,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -18541,7 +20129,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -18654,7 +20242,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -18767,7 +20355,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -18880,7 +20468,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -18993,7 +20581,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -19110,7 +20698,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -19227,7 +20815,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -19236,6 +20824,115 @@
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pan2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MET_copy_gain</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MET FISH-positive vs negative</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2.362</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.163</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4.798</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Pan 2022 Research Square preprint (doi:10.21203/rs.3.rs-1823800/v1); Table 3 univariate (SCRC)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -19253,7 +20950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19456,7 +21153,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -19559,7 +21256,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -19662,7 +21359,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -19670,7 +21367,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Main text gives 12/30 (43.3%), Supplementary Table S4 gives 13/30 (43.3%); table value used</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19765,7 +21466,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -19868,7 +21569,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -19971,7 +21672,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -20074,7 +21775,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -20177,7 +21878,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -20280,7 +21981,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -20383,7 +22084,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -20486,7 +22187,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -20589,7 +22290,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -20692,7 +22393,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -20795,7 +22496,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -20898,7 +22599,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -21001,7 +22702,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -21108,7 +22809,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -21215,7 +22916,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -21322,7 +23023,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -21429,7 +23130,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -21516,7 +23217,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -21611,7 +23312,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>PENDING human second extractor</t>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -21828,6 +23529,113 @@
       <c r="U25" t="inlineStr">
         <is>
           <t>Full text not retrieved; S. mansoni stratum</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pan2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MET FISH-positive</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mean &gt;=3 MET copies/cell</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FISH on TMA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>S_japonicum_presumed</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>calculated_from_percentage</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Pan 2022 Research Square preprint (doi:10.21203/rs.3.rs-1823800/v1); Results (9.2% vs 10.7%; total 34)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Independent blinded second extraction (AI), adjudicated against source 2026-10-05</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Counts from percentages (12+22=34 matches stated total). Preprint; Qingpu cohort (G3)</t>
         </is>
       </c>
     </row>
@@ -21847,7 +23655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23948,7 +25756,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>62.5 vs 47.2%, P&lt;0.05</t>
+          <t>62.5 vs 47.2%; uncorrected chi-square P=0.036 (continuity-corrected P=0.050, printed chi2=3.827)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -24245,6 +26053,422 @@
         </is>
       </c>
       <c r="F75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>age_older</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>66.1 vs 58.4 y; &gt;60 y P&lt;0.001</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ge 2023 Table 1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>male_sex</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>no_difference</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>68.1 vs 59.9%, P=0.106</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ge 2023 Table 1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>rectal_location</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>no_difference</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>location P=0.807</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ge 2023 Table 1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>advanced_stage_III_IV</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>no_difference</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TNM P=0.062</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ge 2023 Table 1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OS_hazard</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>matched cohort, log-rank P=0.005</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ge 2023 Fig. 4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OS_hazard</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>adjusted HR 3.661 (1.458-9.193)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Wang M 2014 Table 3</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DFS_hazard</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>adjusted HR 3.147 (1.359-7.290)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Wang M 2014 Table 3</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>tumor_size_5cm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>mean 4.27 vs 3.33 cm, P=0.017 (continuous)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Wang M 2014 Table 1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>age_older</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>71-80 y 52% vs ~26% (Fig. 4A)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Zhou 2025 Results and Fig. 4</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>male_sex</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>68.4 vs 55.9% (no test reported)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Zhou 2025 Results</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>poor_differentiation</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>no_difference</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>no significant difference (Fig. 4C)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Zhou 2025 Results</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>advanced_stage_III_IV</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>no_difference</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>similar TNM distribution (Fig. 4D)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Zhou 2025 Results</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zhou2025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LN_metastasis</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>28.4 vs 35.8% (no test reported)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Zhou 2025 Results</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -24266,7 +26490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24404,7 +26628,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -24476,7 +26700,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -24513,7 +26737,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -24533,7 +26757,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -24548,12 +26772,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Adjusted OS HR (TNM stage, gender); blinded egg assessment; loss to follow-up NR</t>
+          <t>Adjusted OS HR (TNM stage, gender); blinded egg assessment; loss to follow-up NR; second assessor differed on C1_comparability; consensus 1 star (adjusted for stage and sex, not age), total 7, rating unchanged</t>
         </is>
       </c>
     </row>
@@ -24620,7 +26844,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -24692,7 +26916,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -24764,7 +26988,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -24836,7 +27060,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -24908,7 +27132,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -24980,7 +27204,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDING human second assessor</t>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -25346,6 +27570,150 @@
       <c r="N15" t="inlineStr">
         <is>
           <t>Biomarker comparison unadjusted; same cohort as WangW2020 (286 with evaluable TMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ge2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Survival comparison propensity-matched on stage, age, sex; follow-up to Aug 2022 (median NR; completeness NR); preprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WangM2014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Claude (AI-assisted, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Independent blinded second assessment (AI), 2026-10-05</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Matched on age, sex and stage, adjusted Cox; SACC definition not stated (S3 not awarded); 3/33 SACC lost to follow-up; median FU 49.8 mo</t>
         </is>
       </c>
     </row>
